--- a/branches/fix/invariant-fhirpath-aliases/StructureDefinition-mii-pr-icu-vent-endexpiratorischer-kohlendioxidpartialdruck.xlsx
+++ b/branches/fix/invariant-fhirpath-aliases/StructureDefinition-mii-pr-icu-vent-endexpiratorischer-kohlendioxidpartialdruck.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3729" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3729" uniqueCount="575">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T12:10:38+00:00</t>
+    <t>2026-09-15T13:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}mii-icu-loinc-sct-dgai-ieee11073:Es muss mindestens ein LOINC, SnomedCT, IEEE-11073 oder DGAI Code vorhanden sein {coding.where(system = 'http://loinc.org').exists() or coding.where(system = 'http://snomed.info/sct').exists() or coding.where(system = 'http://dgai.de').exists() or coding.where(system = 'urn:iso:std:iso:11073:10101').exists()}mii-icu-comp-xor-val:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() xor value.exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}mii-icu-comp-xor-val:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() xor value.exists())}</t>
   </si>
   <si>
     <t>Event</t>
@@ -887,6 +887,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+mii-icu-loinc-sct-dgai-ieee11073:Es muss mindestens ein LOINC, SnomedCT, IEEE-11073 oder DGAI Code vorhanden sein {coding.where(system = 'http://loinc.org').exists() or coding.where(system = 'http://snomed.info/sct').exists() or coding.where(system = 'http://dgai.de').exists() or coding.where(system = 'urn:iso:std:iso:11073:10101').exists()}</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -5579,30 +5583,30 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>277</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5714,10 +5718,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5831,10 +5835,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5842,7 +5846,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>79</v>
@@ -5948,13 +5952,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>80</v>
@@ -5998,7 +6002,7 @@
         <v>80</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>80</v>
@@ -6017,7 +6021,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -6067,10 +6071,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6182,10 +6186,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6299,10 +6303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6347,7 +6351,7 @@
         <v>80</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>80</v>
@@ -6418,10 +6422,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6535,10 +6539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6652,10 +6656,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6769,10 +6773,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6888,13 +6892,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>80</v>
@@ -6938,7 +6942,7 @@
         <v>80</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>80</v>
@@ -6957,7 +6961,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>80</v>
@@ -7007,10 +7011,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7122,10 +7126,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7239,10 +7243,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7287,7 +7291,7 @@
         <v>80</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>80</v>
@@ -7358,10 +7362,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7475,10 +7479,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7592,10 +7596,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7709,10 +7713,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7828,13 +7832,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>80</v>
@@ -7878,7 +7882,7 @@
         <v>80</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>80</v>
@@ -7897,7 +7901,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7947,10 +7951,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8062,10 +8066,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8179,10 +8183,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8227,7 +8231,7 @@
         <v>80</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>80</v>
@@ -8298,10 +8302,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8415,10 +8419,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8532,10 +8536,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8649,10 +8653,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8768,10 +8772,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8887,10 +8891,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8913,19 +8917,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8974,7 +8978,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8989,16 +8993,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -9006,10 +9010,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9032,16 +9036,16 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9091,7 +9095,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9112,10 +9116,10 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
@@ -9123,14 +9127,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9149,19 +9153,19 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -9210,7 +9214,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9225,16 +9229,16 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9242,14 +9246,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9268,19 +9272,19 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -9329,7 +9333,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9344,16 +9348,16 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -9361,10 +9365,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9387,16 +9391,16 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9446,7 +9450,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9467,10 +9471,10 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9478,10 +9482,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9504,17 +9508,17 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9563,7 +9567,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9578,16 +9582,16 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -9595,10 +9599,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9621,19 +9625,19 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9643,7 +9647,7 @@
         <v>80</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>80</v>
@@ -9682,7 +9686,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9691,7 +9695,7 @@
         <v>90</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>102</v>
@@ -9700,24 +9704,24 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9829,10 +9833,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9946,10 +9950,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9972,19 +9976,19 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10033,7 +10037,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10054,7 +10058,7 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>80</v>
@@ -10065,10 +10069,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10094,20 +10098,20 @@
         <v>110</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q68" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="R68" t="s" s="2">
         <v>80</v>
@@ -10131,10 +10135,10 @@
         <v>174</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10152,7 +10156,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10173,7 +10177,7 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>80</v>
@@ -10184,10 +10188,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10213,14 +10217,14 @@
         <v>199</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10269,7 +10273,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10290,7 +10294,7 @@
         <v>80</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>80</v>
@@ -10301,10 +10305,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10330,14 +10334,14 @@
         <v>104</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10347,7 +10351,7 @@
         <v>80</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>80</v>
@@ -10386,7 +10390,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10395,7 +10399,7 @@
         <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>102</v>
@@ -10407,7 +10411,7 @@
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>80</v>
@@ -10418,10 +10422,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10447,16 +10451,16 @@
         <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -10505,7 +10509,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10526,7 +10530,7 @@
         <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>80</v>
@@ -10537,10 +10541,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10566,16 +10570,16 @@
         <v>182</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
@@ -10600,13 +10604,13 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -10624,7 +10628,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10633,7 +10637,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -10645,7 +10649,7 @@
         <v>80</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>80</v>
@@ -10656,14 +10660,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10685,16 +10689,16 @@
         <v>182</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -10719,13 +10723,13 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10743,7 +10747,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10761,24 +10765,24 @@
         <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10801,19 +10805,19 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -10862,7 +10866,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10883,7 +10887,7 @@
         <v>80</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>80</v>
@@ -10894,10 +10898,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10923,13 +10927,13 @@
         <v>182</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10955,11 +10959,11 @@
         <v>80</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
@@ -10977,7 +10981,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10995,24 +10999,24 @@
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11038,16 +11042,16 @@
         <v>182</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11075,10 +11079,10 @@
         <v>274</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>80</v>
@@ -11096,7 +11100,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11117,7 +11121,7 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>80</v>
@@ -11128,10 +11132,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11154,16 +11158,16 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11213,7 +11217,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11231,24 +11235,24 @@
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11271,16 +11275,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11330,7 +11334,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11348,24 +11352,24 @@
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11388,19 +11392,19 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11449,7 +11453,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11461,7 +11465,7 @@
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -11470,7 +11474,7 @@
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>80</v>
@@ -11481,10 +11485,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11596,10 +11600,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11713,14 +11717,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11742,10 +11746,10 @@
         <v>134</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>137</v>
@@ -11800,7 +11804,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11832,10 +11836,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11858,13 +11862,13 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11915,7 +11919,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11924,7 +11928,7 @@
         <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>102</v>
@@ -11936,7 +11940,7 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>80</v>
@@ -11947,10 +11951,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11973,13 +11977,13 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12030,7 +12034,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12039,7 +12043,7 @@
         <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>102</v>
@@ -12051,7 +12055,7 @@
         <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>80</v>
@@ -12062,10 +12066,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12091,16 +12095,16 @@
         <v>182</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
@@ -12128,10 +12132,10 @@
         <v>114</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>80</v>
@@ -12149,7 +12153,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12167,10 +12171,10 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>80</v>
@@ -12181,10 +12185,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12210,16 +12214,16 @@
         <v>182</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12247,10 +12251,10 @@
         <v>274</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>80</v>
@@ -12268,7 +12272,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12286,10 +12290,10 @@
         <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>80</v>
@@ -12300,10 +12304,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12326,17 +12330,17 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12385,7 +12389,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12417,10 +12421,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12446,10 +12450,10 @@
         <v>199</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12500,7 +12504,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12521,7 +12525,7 @@
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>80</v>
@@ -12532,10 +12536,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12558,16 +12562,16 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12617,7 +12621,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12638,7 +12642,7 @@
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>80</v>
@@ -12649,10 +12653,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12675,16 +12679,16 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12734,7 +12738,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12755,7 +12759,7 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>80</v>
@@ -12766,10 +12770,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12792,19 +12796,19 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -12853,7 +12857,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12874,7 +12878,7 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>80</v>
@@ -12885,10 +12889,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13000,10 +13004,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13117,14 +13121,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13146,10 +13150,10 @@
         <v>134</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>137</v>
@@ -13204,7 +13208,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13236,10 +13240,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13265,13 +13269,13 @@
         <v>182</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>273</v>
@@ -13323,7 +13327,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>90</v>
@@ -13341,13 +13345,13 @@
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13355,10 +13359,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13381,19 +13385,19 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -13442,7 +13446,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13460,24 +13464,24 @@
         <v>80</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13503,16 +13507,16 @@
         <v>182</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>80</v>
@@ -13537,13 +13541,13 @@
         <v>80</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>80</v>
@@ -13561,7 +13565,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13570,7 +13574,7 @@
         <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>102</v>
@@ -13582,7 +13586,7 @@
         <v>80</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>80</v>
@@ -13593,14 +13597,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13622,16 +13626,16 @@
         <v>182</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>80</v>
@@ -13656,13 +13660,13 @@
         <v>80</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>80</v>
@@ -13680,7 +13684,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13698,24 +13702,24 @@
         <v>80</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13741,16 +13745,16 @@
         <v>81</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>80</v>
@@ -13799,7 +13803,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13820,7 +13824,7 @@
         <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>80</v>
